--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0003T0006Z000C1N18_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0003T0006Z000C1N18_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.13294543356923</v>
+        <v>8.309103632955001</v>
       </c>
       <c r="D2" t="n">
-        <v>51.01209566423353</v>
+        <v>8.289465545437949</v>
       </c>
       <c r="E2" t="n">
-        <v>9.528494829657401</v>
+        <v>1.548380409819328</v>
       </c>
       <c r="F2" t="n">
-        <v>19.37930685362197</v>
+        <v>3.14913736371357</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.23840538485069</v>
+        <v>6.051240875038236</v>
       </c>
       <c r="D3" t="n">
-        <v>36.77635865144015</v>
+        <v>5.976158280859024</v>
       </c>
       <c r="E3" t="n">
-        <v>9.528494829657401</v>
+        <v>1.548380409819328</v>
       </c>
       <c r="F3" t="n">
-        <v>19.37930685362197</v>
+        <v>3.14913736371357</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>59.89386641687745</v>
+        <v>9.732753292742586</v>
       </c>
       <c r="D4" t="n">
-        <v>13.05693683957653</v>
+        <v>2.121752236431186</v>
       </c>
       <c r="E4" t="n">
-        <v>9.528494829657401</v>
+        <v>1.548380409819328</v>
       </c>
       <c r="F4" t="n">
-        <v>19.37930685362197</v>
+        <v>3.14913736371357</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>43.3436407261688</v>
+        <v>7.04334161800243</v>
       </c>
       <c r="D5" t="n">
-        <v>17.70362810605608</v>
+        <v>2.876839567234113</v>
       </c>
       <c r="E5" t="n">
-        <v>9.528494829657401</v>
+        <v>1.548380409819328</v>
       </c>
       <c r="F5" t="n">
-        <v>19.37930685362197</v>
+        <v>3.14913736371357</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.61835832896002</v>
+        <v>6.437983228456003</v>
       </c>
       <c r="D6" t="n">
-        <v>13.58307770720612</v>
+        <v>2.207250127420995</v>
       </c>
       <c r="E6" t="n">
-        <v>9.528494829657401</v>
+        <v>1.548380409819328</v>
       </c>
       <c r="F6" t="n">
-        <v>19.37930685362197</v>
+        <v>3.14913736371357</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>61.78072077349797</v>
+        <v>10.03936712569342</v>
       </c>
       <c r="D7" t="n">
-        <v>63.1195289455594</v>
+        <v>10.2569234536534</v>
       </c>
       <c r="E7" t="n">
-        <v>9.528494829657401</v>
+        <v>1.548380409819328</v>
       </c>
       <c r="F7" t="n">
-        <v>19.37930685362197</v>
+        <v>3.14913736371357</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
